--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -451,7 +451,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Encounter.extension:associatedEncounter</t>
@@ -827,7 +827,7 @@
 </t>
   </si>
   <si>
-    <t>この遭遇が記録されるべきケアのエピソード</t>
+    <t>このEnounterが記録されるべきケアのエピソード</t>
   </si>
   <si>
     <t>特定のエピソードの一部として特定のエンカウンターを分類する必要がある場合、このフィールドを使用する必要があります。この関連は、政府報告、問題追跡、共通の課題に関連するエンカウンターを特定の目的のためにグループ化するのに役立ちます。これらの関連は、通常、エピソードの後に作成され、新しいエンカウンターを追加するためにエピソードを編集するのではなく、入力時にグループ化されます（エピソードは数年にわたって広がる可能性があります）。</t>
@@ -868,7 +868,7 @@
     <t>Encounter.participant</t>
   </si>
   <si>
-    <t>遭遇に関わった参加者のリスト</t>
+    <t>Enounterに関わった参加者のリスト</t>
   </si>
   <si>
     <t>サービスを提供する責任を持つ人々のリスト</t>
@@ -1190,7 +1190,7 @@
     <t>Encounter.hospitalization.preAdmissionIdentifier</t>
   </si>
   <si>
-    <t>事前入院identifier (Jizen nyugaku shikibetsushi)</t>
+    <t>事前入院identifier</t>
   </si>
   <si>
     <t>入院前のidentifier</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
@@ -648,13 +648,13 @@
 </t>
   </si>
   <si>
-    <t>患者とのEncounterの分類【詳細参照】</t>
+    <t>患者との受療行動の分類【詳細参照】</t>
   </si>
   <si>
     <t>外来（外来）、入院、救急、在宅医療、その他の地域差による患者Encounterの分類を表す概念。</t>
   </si>
   <si>
-    <t>コードは列挙やコードリストの中で非常にカジュアルに定義されることもあれば、SNOMED CTのような非常にフォーマルな定義まである。 - 詳細はHL7 v3コア・プリンシプルを参照すること。</t>
+    <t>コードは列挙やコードリストの中で非常にカジュアルに定義されることもあれば、SNOMED CTのような非常にフォーマルな定義まである。 - 詳細は[HL7 v3コア・プリンシプル](https://www.hl7.org/implement/standards/product_brief.cfm?product_id=481)を参照すること。</t>
   </si>
   <si>
     <t>extensible</t>
@@ -703,7 +703,7 @@
 入院｜外来｜外来｜救急＋。</t>
   </si>
   <si>
-    <t>コードは列挙やコードリストの中で非常にカジュアルに定義されることもあれば、SNOMED CTのような非常にフォーマルな定義まである- 詳細はHL7 v3コア・プリンシプルを参照すること。</t>
+    <t>コードは列挙やコードリストの中で非常にカジュアルに定義されることもあれば、SNOMED CTのような非常にフォーマルな定義まである- 詳細は[HL7 v3コア・プリンシプル](https://www.hl7.org/implement/standards/product_brief.cfm?product_id=481)を参照すること。</t>
   </si>
   <si>
     <t>Encounter.classHistory.period</t>
@@ -1058,7 +1058,7 @@
     <t>Encounter.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition_Diagnosis|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Common|ImmunizationRecommendation)
 </t>
   </si>
   <si>
@@ -1093,7 +1093,7 @@
 discharge diagnosisindication</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Condition_Diagnosis|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure)
 </t>
   </si>
   <si>
@@ -1809,7 +1809,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="207.359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="473">
   <si>
     <t>Property</t>
   </si>
@@ -534,7 +534,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>Encounter（診察、受診、入退院など）の現状。</t>
+    <t>受療行動の現状。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-status|4.0.1</t>
@@ -660,7 +660,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>Encounter（診察、受診、入退院など）の分類。</t>
+    <t>受療行動の分類。</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActEncounterCode</t>
@@ -722,19 +722,19 @@
 </t>
   </si>
   <si>
-    <t>特定の種類のEncounter（診察、受診、入退院など）</t>
-  </si>
-  <si>
-    <t>特定のEncounter（診察、受診、入退院など）の種類（例：メール相談、手術日帰り、スキルド・ナーシング、リハビリテーション）</t>
-  </si>
-  <si>
-    <t>Encounter（診察、受診、入退院など）をさらに分類する方法が多数存在するため、この要素は0から複数の値をとる。</t>
+    <t>特定の受療行動の種類</t>
+  </si>
+  <si>
+    <t>特定の受療行動の種類の種類（例：メール相談、手術日帰り、スキルド・ナーシング、リハビリテーション）</t>
+  </si>
+  <si>
+    <t>受療行動をさらに分類する方法が多数存在するため、この要素は0から複数の値をとる。</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>Encounter（診察、受診、入退院など）のタイプ。</t>
+    <t>受療行動のタイプ。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-type</t>
@@ -770,10 +770,10 @@
     <t>Encounter.priority</t>
   </si>
   <si>
-    <t>Encounter（診察、受診、入退院など）の緊急性を示す</t>
-  </si>
-  <si>
-    <t>Encounter（診察、受診、入退院など）の緊急性を示します。</t>
+    <t>受療行動の緊急性を示す</t>
+  </si>
+  <si>
+    <t>受療行動の緊急性を示します。</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActPriority</t>
@@ -799,10 +799,10 @@
 </t>
   </si>
   <si>
-    <t>対面時に出席している患者またはグループ</t>
-  </si>
-  <si>
-    <t>診察時に存在する患者またはグループ。</t>
+    <t>受療した患者またはグループ</t>
+  </si>
+  <si>
+    <t>受療した患者またはグループ。</t>
   </si>
   <si>
     <t>エンカウンターは常に患者に関するものですが、すべての使用状況で患者が実際に知られていない場合があり、匿名である可能性があります（例えばアルコール依存症のグループセラピーの場合- エンカウンターの記録が人数/スタッフの請求に使用され、特定の患者の文脈に重要ではない場合、または獣医治療では、個々に追跡されていない群れの羊が治療を受ける場合があります）。</t>
@@ -827,7 +827,7 @@
 </t>
   </si>
   <si>
-    <t>このEnounterが記録されるべきケアのエピソード</t>
+    <t>この受療行動が記録されるべきケアのエピソード</t>
   </si>
   <si>
     <t>特定のエピソードの一部として特定のエンカウンターを分類する必要がある場合、このフィールドを使用する必要があります。この関連は、政府報告、問題追跡、共通の課題に関連するエンカウンターを特定の目的のためにグループ化するのに役立ちます。これらの関連は、通常、エピソードの後に作成され、新しいエンカウンターを追加するためにエピソードを編集するのではなく、入力時にグループ化されます（エピソードは数年にわたって広がる可能性があります）。</t>
@@ -853,10 +853,10 @@
 </t>
   </si>
   <si>
-    <t>このEncounter（診察、受診、入退院など）を開始したサービスリクエスト</t>
-  </si>
-  <si>
-    <t>このEncounter（診察、受診、入退院など）が満たす要請（例：紹介依頼や手続き要請）</t>
+    <t>この受療行動を開始したサービスリクエスト</t>
+  </si>
+  <si>
+    <t>この受療行動が満たす要請（例：紹介依頼や手続き要請）</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -868,7 +868,7 @@
     <t>Encounter.participant</t>
   </si>
   <si>
-    <t>Enounterに関わった参加者のリスト</t>
+    <t>受療行動に関わった参加者のリスト</t>
   </si>
   <si>
     <t>サービスを提供する責任を持つ人々のリスト</t>
@@ -895,10 +895,10 @@
     <t>Encounter.participant.type</t>
   </si>
   <si>
-    <t>Encounter（診察、受診、入退院など）における参加者の役割</t>
-  </si>
-  <si>
-    <t>Encounter（診察、受診、入退院など）における参加者の役割。</t>
+    <t>受療行動における参加者の役割</t>
+  </si>
+  <si>
+    <t>受療行動における参加者の役割。</t>
   </si>
   <si>
     <t>参加者タイプは、個人がどのようにエンカウントに参加するかを示します。それには、非開業者の参加者が含まれ、開業者にとってはこのエンカウントの文脈でアクションタイプを説明することが含まれます（例：入院医師、診療医師、翻訳者、相談医師）。これは、雇用、教育、免許などの用語から派生した機能的な役割である開業者の役割とは異なります。</t>
@@ -919,7 +919,7 @@
     <t>Encounter.participant.period</t>
   </si>
   <si>
-    <t>参加者が参加したエンカウンターの期間</t>
+    <t>受療行動の期間</t>
   </si>
   <si>
     <t>指定された参加者が出席した期間。これらは重複することがあり、全体的なエンカウント期間のサブセットになることもあります。</t>
@@ -941,7 +941,7 @@
     <t>患者以外に関与する人</t>
   </si>
   <si>
-    <t>患者以外にEncounter（診察、受診、入退院など）に関わった人々。</t>
+    <t>患者以外に受療行動に関わった人々。</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -963,10 +963,10 @@
 </t>
   </si>
   <si>
-    <t>このEncounter（診察、受診、入退院など）を予定した予約</t>
-  </si>
-  <si>
-    <t>このEncounter（診察、受診、入退院など）を予定した約束。</t>
+    <t>この受療行動を予定した予約</t>
+  </si>
+  <si>
+    <t>この受療行動を予定した約束。</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=FLFS].target[classCode=ENC, moodCode=APT]</t>
@@ -978,10 +978,10 @@
     <t>Encounter.period</t>
   </si>
   <si>
-    <t>Encounter（診察、受診、入退院など）の始まりと終わりの時間</t>
-  </si>
-  <si>
-    <t>Encounter（診察、受診、入退院など）の開始時刻と終了時刻。</t>
+    <t>受療行動の始まりと終わりの時間</t>
+  </si>
+  <si>
+    <t>受療行動の開始時刻と終了時刻。</t>
   </si>
   <si>
     <t>もし、まだ知られていなければ、期間の終わりは省略できます。</t>
@@ -1006,7 +1006,7 @@
 </t>
   </si>
   <si>
-    <t>Encounter（診察、受診、入退院など）が続いた時間（不在時間を差し引いた時間）</t>
+    <t>受療行動が続いた時間（不在時間を差し引いた時間）</t>
   </si>
   <si>
     <t>接触が続いた時間の量です。休暇中の時間は除かれます。</t>
@@ -1031,13 +1031,13 @@
     <t>エンカウントが生じる理由がコード化されている</t>
   </si>
   <si>
-    <t>Encounter（診察、受診、入退院など）が起こる理由をコードとして表現します。入院に関しては、コード化された入院診断に使用できます。</t>
+    <t>受療行動が起こる理由をコードとして表現します。入院に関しては、コード化された入院診断に使用できます。</t>
   </si>
   <si>
     <t>主要な診断を知る必要があるシステムには、標準拡張子primaryDiagnosis（フラグではなく、シーケンス値である1 = 主要な診断）でマークされます。</t>
   </si>
   <si>
-    <t>Encounter（診察、受診、入退院など）が起こる理由。</t>
+    <t>受療行動が起こる理由。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-reason</t>
@@ -1062,7 +1062,7 @@
 </t>
   </si>
   <si>
-    <t>Encounter（診察、受診、入退院など）が生じた理由（参照）</t>
+    <t>受療行動が生じた理由（参照）</t>
   </si>
   <si>
     <t>Encounter.diagnosis</t>
@@ -1118,7 +1118,7 @@
     <t>この診断に対する役割（入院、請求、退院など）</t>
   </si>
   <si>
-    <t>この診断がEncounter（診察、受診、入退院など）の中で果たす役割（入院、請求、退院など）</t>
+    <t>この診断が受療行動の中で果たす役割（入院、請求、退院など）</t>
   </si>
   <si>
     <t>この状態が表す診断のタイプ。</t>
@@ -1156,7 +1156,7 @@
     <t>このエンカウンターの請求に使用できるアカウントのセット。</t>
   </si>
   <si>
-    <t>請求システムは内部のビジネスルールに基づいて、Encounter（診察、受診、入退院など）に関連する請求可能なアイテムを複数の参照されたアカウントに割り当てることができます。</t>
+    <t>請求システムは内部のビジネスルールに基づいて、受療行動に関連する請求可能なアイテムを複数の参照されたアカウントに割り当てることができます。</t>
   </si>
   <si>
     <t>.pertains.A_Account</t>
@@ -1190,7 +1190,7 @@
     <t>Encounter.hospitalization.preAdmissionIdentifier</t>
   </si>
   <si>
-    <t>事前入院identifier</t>
+    <t>事前入院のidentifier</t>
   </si>
   <si>
     <t>入院前のidentifier</t>
@@ -1218,15 +1218,9 @@
     <t>Encounter.hospitalization.admitSource</t>
   </si>
   <si>
-    <t>患者が入院した場所（医師の紹介、転院）</t>
-  </si>
-  <si>
     <t>患者がどこから入院したのか（医師の紹介、転院）</t>
   </si>
   <si>
-    <t>患者が入院した場所はどこですか。</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-admit-source</t>
   </si>
   <si>
@@ -1347,9 +1341,6 @@
     <t>退院後の場所のカテゴリーまたは種類。</t>
   </si>
   <si>
-    <t>退院時の配慮。</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/encounter-discharge-disposition</t>
   </si>
   <si>
@@ -1362,10 +1353,10 @@
     <t>Encounter.location</t>
   </si>
   <si>
-    <t>患者が行った場所のリスト</t>
-  </si>
-  <si>
-    <t>この接触中に患者が滞在した場所のリスト</t>
+    <t>患者が滞在した場所のリスト</t>
+  </si>
+  <si>
+    <t>この受療行動中に患者が滞在した場所のリスト</t>
   </si>
   <si>
     <t>エンカウント」には、場所の種類である「クライアントの自宅」のような場所の参照を明示することで、バーチャルなエンカウントを記録できます。また、エンカウントクラスは「バーチャル」である必要があります。</t>
@@ -1390,10 +1381,10 @@
 </t>
   </si>
   <si>
-    <t>Encounter（診察、受診、入退院など）の場所</t>
-  </si>
-  <si>
-    <t>Encounter（診察、受診、入退院など）が起こる場所。</t>
+    <t>受療行動の場所</t>
+  </si>
+  <si>
+    <t>受療行動が起こる場所。</t>
   </si>
   <si>
     <t>Event.location</t>
@@ -1429,7 +1420,7 @@
     <t>Encounter.location.physicalType</t>
   </si>
   <si>
-    <t>場所の物理的なタイプ（通常は場所の階層のレベル、ベッドルームワードなど）</t>
+    <t>場所の物理的なタイプ（ベッド/病室/部屋など）</t>
   </si>
   <si>
     <t>これは、メッセージングまたはクエリを簡素化するために記録が必要なレベル（ベッド/病室/部屋など）を特定するために使用されます。</t>
@@ -1448,10 +1439,7 @@
     <t>Encounter.location.period</t>
   </si>
   <si>
-    <t>患者が場所にいた期間</t>
-  </si>
-  <si>
-    <t>患者が場所にいた期間。</t>
+    <t>患者がその場所にいた期間</t>
   </si>
   <si>
     <t>Encounter.serviceProvider</t>
@@ -1461,7 +1449,7 @@
 </t>
   </si>
   <si>
-    <t>このEncounter（診察、受診、入退院など）に責任を持つ組織（施設）</t>
+    <t>この受療行動に責任を持つ組織（施設）</t>
   </si>
   <si>
     <t>このエンカウンターのサービスを主に担当する組織。これは患者の記録にある組織と同じかもしれませんが、外部組織からサービスを提供するアクターがいる場合など、別の組織である可能性もあります(別途請求される可能性があります)。大腸内視鏡検査の簡略化されたエンカウンターのBundleを参照してください。</t>
@@ -1480,10 +1468,10 @@
 </t>
   </si>
   <si>
-    <t>もう一度のEncounter（診察、受診、入退院など）。このEncounter（診察、受診、入退院など）は一部である。</t>
-  </si>
-  <si>
-    <t>このEncounter（診察、受診、入退院など）が一部である、別のEncounter（診察、受診、入退院など）（手続き的にも時間的にも）。</t>
+    <t>もう一度の受療行動。この受療行動は一部である。</t>
+  </si>
+  <si>
+    <t>この受療行動が一部である、別の受療行動（手続き的にも時間的にも）。</t>
   </si>
   <si>
     <t>これは、子供の経験を母親の経験に関連付けるためにも使用されます。詳細については、患者リソースのノートセクションを参照してください。</t>
@@ -8458,7 +8446,7 @@
         <v>386</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8488,10 +8476,10 @@
         <v>113</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>81</v>
@@ -8527,21 +8515,21 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8567,10 +8555,10 @@
         <v>225</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8600,10 +8588,10 @@
         <v>229</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -8621,7 +8609,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8645,15 +8633,15 @@
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8679,16 +8667,16 @@
         <v>225</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -8716,10 +8704,10 @@
         <v>229</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -8737,7 +8725,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8755,21 +8743,21 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8795,10 +8783,10 @@
         <v>225</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8828,10 +8816,10 @@
         <v>113</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -8849,7 +8837,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8867,21 +8855,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8907,10 +8895,10 @@
         <v>225</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8940,10 +8928,10 @@
         <v>113</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -8961,7 +8949,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8979,21 +8967,21 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9019,10 +9007,10 @@
         <v>381</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9073,7 +9061,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9091,21 +9079,21 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9131,10 +9119,10 @@
         <v>225</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9164,10 +9152,10 @@
         <v>229</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>81</v>
@@ -9185,7 +9173,7 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9203,21 +9191,21 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9243,13 +9231,13 @@
         <v>173</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9299,7 +9287,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9317,7 +9305,7 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -9328,10 +9316,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9440,10 +9428,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9554,10 +9542,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9670,10 +9658,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9696,13 +9684,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9753,7 +9741,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>89</v>
@@ -9768,24 +9756,24 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>299</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9811,13 +9799,13 @@
         <v>109</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9846,10 +9834,10 @@
         <v>165</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -9867,7 +9855,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9885,7 +9873,7 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -9896,10 +9884,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9925,13 +9913,13 @@
         <v>225</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9960,10 +9948,10 @@
         <v>229</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -9981,7 +9969,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10010,10 +9998,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10039,10 +10027,10 @@
         <v>196</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10093,7 +10081,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10122,10 +10110,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10148,13 +10136,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10205,7 +10193,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10223,21 +10211,21 @@
         <v>298</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10260,16 +10248,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10319,7 +10307,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10334,10 +10322,10 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2716" uniqueCount="474">
   <si>
     <t>Property</t>
   </si>
@@ -460,15 +460,19 @@
     <t>associatedEncounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {encounter-associatedEncounter}
+    <t xml:space="preserve">Extension {encounter-associatedEncounter|4.0.1}
 </t>
   </si>
   <si>
     <t>関連するEncounter</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Encounter.modifierExtension</t>
@@ -2950,10 +2954,10 @@
         <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -2970,14 +2974,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2999,16 +3003,16 @@
         <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>81</v>
@@ -3057,7 +3061,7 @@
         <v>81</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3086,10 +3090,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3112,13 +3116,13 @@
         <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3169,7 +3173,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3184,24 +3188,24 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3227,13 +3231,13 @@
         <v>109</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3259,13 +3263,13 @@
         <v>81</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>81</v>
@@ -3283,7 +3287,7 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>89</v>
@@ -3298,24 +3302,24 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3338,16 +3342,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3397,7 +3401,7 @@
         <v>81</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3415,7 +3419,7 @@
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>81</v>
@@ -3426,10 +3430,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3452,13 +3456,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3509,7 +3513,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3527,7 +3531,7 @@
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>81</v>
@@ -3538,14 +3542,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3567,13 +3571,13 @@
         <v>134</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3623,7 +3627,7 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3641,7 +3645,7 @@
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>81</v>
@@ -3652,14 +3656,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3681,16 +3685,16 @@
         <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3739,7 +3743,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3768,10 +3772,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3797,13 +3801,13 @@
         <v>109</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3829,13 +3833,13 @@
         <v>81</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>81</v>
@@ -3853,7 +3857,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>89</v>
@@ -3871,7 +3875,7 @@
         <v>81</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>81</v>
@@ -3882,10 +3886,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3908,16 +3912,16 @@
         <v>81</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3967,7 +3971,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>89</v>
@@ -3985,7 +3989,7 @@
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>81</v>
@@ -3996,10 +4000,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4022,16 +4026,16 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4057,13 +4061,13 @@
         <v>81</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>81</v>
@@ -4081,7 +4085,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>89</v>
@@ -4099,21 +4103,21 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4136,13 +4140,13 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4193,7 +4197,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4211,7 +4215,7 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>81</v>
@@ -4222,10 +4226,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4248,13 +4252,13 @@
         <v>81</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4305,7 +4309,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4323,7 +4327,7 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>81</v>
@@ -4334,14 +4338,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4363,13 +4367,13 @@
         <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4419,7 +4423,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4437,7 +4441,7 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>81</v>
@@ -4448,14 +4452,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4477,16 +4481,16 @@
         <v>134</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4535,7 +4539,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4564,10 +4568,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4590,16 +4594,16 @@
         <v>81</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4625,13 +4629,13 @@
         <v>81</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>81</v>
@@ -4649,7 +4653,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>89</v>
@@ -4667,7 +4671,7 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>81</v>
@@ -4678,10 +4682,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4704,16 +4708,16 @@
         <v>81</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4763,7 +4767,7 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>89</v>
@@ -4781,7 +4785,7 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>81</v>
@@ -4792,10 +4796,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4818,16 +4822,16 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4853,13 +4857,13 @@
         <v>81</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>81</v>
@@ -4877,7 +4881,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4892,24 +4896,24 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4932,13 +4936,13 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4965,13 +4969,13 @@
         <v>81</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>81</v>
@@ -4989,7 +4993,7 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5004,24 +5008,24 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5044,13 +5048,13 @@
         <v>81</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5077,13 +5081,13 @@
         <v>81</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>81</v>
@@ -5101,7 +5105,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5119,25 +5123,25 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5156,16 +5160,16 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5215,7 +5219,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5230,24 +5234,24 @@
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5270,13 +5274,13 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5327,7 +5331,7 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5342,28 +5346,28 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5382,13 +5386,13 @@
         <v>81</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5439,7 +5443,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5454,10 +5458,10 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>81</v>
@@ -5468,10 +5472,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5494,13 +5498,13 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5551,7 +5555,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5566,24 +5570,24 @@
         <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5606,13 +5610,13 @@
         <v>81</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5663,7 +5667,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5681,7 +5685,7 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>81</v>
@@ -5692,14 +5696,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5721,13 +5725,13 @@
         <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5777,7 +5781,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5795,7 +5799,7 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>81</v>
@@ -5806,14 +5810,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5835,16 +5839,16 @@
         <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5893,7 +5897,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5922,10 +5926,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5948,16 +5952,16 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5983,13 +5987,13 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>81</v>
@@ -6007,7 +6011,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6022,24 +6026,24 @@
         <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6062,13 +6066,13 @@
         <v>81</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6119,7 +6123,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6137,21 +6141,21 @@
         <v>81</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6174,13 +6178,13 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6231,7 +6235,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6246,24 +6250,24 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6286,13 +6290,13 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6343,7 +6347,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6358,24 +6362,24 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6398,16 +6402,16 @@
         <v>81</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6457,7 +6461,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6472,24 +6476,24 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6512,16 +6516,16 @@
         <v>81</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6571,7 +6575,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6586,28 +6590,28 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6626,16 +6630,16 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6664,10 +6668,10 @@
         <v>113</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>81</v>
@@ -6685,7 +6689,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6700,28 +6704,28 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6740,16 +6744,16 @@
         <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6799,7 +6803,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6814,24 +6818,24 @@
         <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6854,13 +6858,13 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6911,7 +6915,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6929,7 +6933,7 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>81</v>
@@ -6940,10 +6944,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6966,13 +6970,13 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7023,7 +7027,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7041,7 +7045,7 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>81</v>
@@ -7052,14 +7056,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7081,13 +7085,13 @@
         <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7137,7 +7141,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7155,7 +7159,7 @@
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>81</v>
@@ -7166,14 +7170,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7195,16 +7199,16 @@
         <v>134</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7253,7 +7257,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7282,14 +7286,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7308,16 +7312,16 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7367,7 +7371,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -7382,24 +7386,24 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7422,13 +7426,13 @@
         <v>81</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7458,10 +7462,10 @@
         <v>113</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>81</v>
@@ -7479,7 +7483,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7497,7 +7501,7 @@
         <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>81</v>
@@ -7508,10 +7512,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7534,13 +7538,13 @@
         <v>81</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7591,7 +7595,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7609,7 +7613,7 @@
         <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>81</v>
@@ -7620,10 +7624,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7646,16 +7650,16 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7705,7 +7709,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7723,7 +7727,7 @@
         <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>81</v>
@@ -7734,10 +7738,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7760,16 +7764,16 @@
         <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7819,7 +7823,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -7837,7 +7841,7 @@
         <v>81</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>81</v>
@@ -7848,10 +7852,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7874,13 +7878,13 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7931,7 +7935,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7949,7 +7953,7 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>81</v>
@@ -7960,14 +7964,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7989,13 +7993,13 @@
         <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8045,7 +8049,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8063,7 +8067,7 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>81</v>
@@ -8074,14 +8078,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8103,16 +8107,16 @@
         <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8161,7 +8165,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8190,10 +8194,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8216,13 +8220,13 @@
         <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8273,7 +8277,7 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -8291,21 +8295,21 @@
         <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8328,13 +8332,13 @@
         <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8385,7 +8389,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8403,7 +8407,7 @@
         <v>81</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>81</v>
@@ -8414,10 +8418,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8440,13 +8444,13 @@
         <v>81</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8476,28 +8480,28 @@
         <v>113</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8515,21 +8519,21 @@
         <v>81</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8552,13 +8556,13 @@
         <v>81</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8585,13 +8589,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -8609,7 +8613,7 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -8627,21 +8631,21 @@
         <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8664,19 +8668,19 @@
         <v>81</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -8701,13 +8705,13 @@
         <v>81</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>81</v>
@@ -8725,7 +8729,7 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -8743,21 +8747,21 @@
         <v>81</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8780,13 +8784,13 @@
         <v>81</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8816,10 +8820,10 @@
         <v>113</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>81</v>
@@ -8837,7 +8841,7 @@
         <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -8855,21 +8859,21 @@
         <v>81</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8892,13 +8896,13 @@
         <v>81</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8928,10 +8932,10 @@
         <v>113</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>81</v>
@@ -8949,7 +8953,7 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -8967,21 +8971,21 @@
         <v>81</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9004,13 +9008,13 @@
         <v>81</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9061,7 +9065,7 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9079,21 +9083,21 @@
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9116,13 +9120,13 @@
         <v>81</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9149,31 +9153,31 @@
         <v>81</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9191,21 +9195,21 @@
         <v>81</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9228,16 +9232,16 @@
         <v>81</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9287,7 +9291,7 @@
         <v>81</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9305,7 +9309,7 @@
         <v>81</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>81</v>
@@ -9316,10 +9320,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9342,13 +9346,13 @@
         <v>81</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9399,7 +9403,7 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9417,7 +9421,7 @@
         <v>81</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>81</v>
@@ -9428,14 +9432,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9457,13 +9461,13 @@
         <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9513,7 +9517,7 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -9531,7 +9535,7 @@
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>81</v>
@@ -9542,14 +9546,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9571,16 +9575,16 @@
         <v>134</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>81</v>
@@ -9629,7 +9633,7 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -9658,10 +9662,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9684,13 +9688,13 @@
         <v>81</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9741,7 +9745,7 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>89</v>
@@ -9756,24 +9760,24 @@
         <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9799,13 +9803,13 @@
         <v>109</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9831,13 +9835,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -9855,7 +9859,7 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -9873,7 +9877,7 @@
         <v>81</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>81</v>
@@ -9884,10 +9888,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9910,16 +9914,16 @@
         <v>81</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9945,13 +9949,13 @@
         <v>81</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>81</v>
@@ -9969,7 +9973,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -9998,10 +10002,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10024,13 +10028,13 @@
         <v>81</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10081,7 +10085,7 @@
         <v>81</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10099,7 +10103,7 @@
         <v>81</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>81</v>
@@ -10110,10 +10114,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10136,13 +10140,13 @@
         <v>81</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10193,7 +10197,7 @@
         <v>81</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10208,24 +10212,24 @@
         <v>101</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10248,16 +10252,16 @@
         <v>81</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10307,7 +10311,7 @@
         <v>81</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10322,10 +10326,10 @@
         <v>101</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
